--- a/tt.xlsx
+++ b/tt.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ethan.li\Documents\test_bc_in_sourcetree\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{286FE49B-1B0E-4E6B-AC73-FF7B8818AA71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -14,18 +20,37 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="1">
+  <si>
+    <t>A</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -53,7 +78,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -330,10 +355,22 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/tt.xlsx
+++ b/tt.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ethan.li\Documents\temp\test_bc_in_sourcetree\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D74C90C-08C8-42D7-AE04-F81C76C7950C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -14,18 +20,37 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="1">
+  <si>
+    <t>a</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -53,7 +78,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -330,10 +355,22 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C9" t="s">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/tt.xlsx
+++ b/tt.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ethan.li\Documents\test_bc_in_sourcetree\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{286FE49B-1B0E-4E6B-AC73-FF7B8818AA71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{017502E3-8C61-45D3-B84E-54B77DA1A221}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,9 +28,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="1">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="1">
   <si>
-    <t>A</t>
+    <t>a</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -356,16 +356,942 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:H36"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" t="s">
+        <v>0</v>
+      </c>
+      <c r="F2" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2" t="s">
+        <v>0</v>
+      </c>
+      <c r="H2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>0</v>
+      </c>
       <c r="B3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" t="s">
+        <v>0</v>
+      </c>
+      <c r="F3" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3" t="s">
+        <v>0</v>
+      </c>
+      <c r="H3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" t="s">
+        <v>0</v>
+      </c>
+      <c r="E4" t="s">
+        <v>0</v>
+      </c>
+      <c r="F4" t="s">
+        <v>0</v>
+      </c>
+      <c r="G4" t="s">
+        <v>0</v>
+      </c>
+      <c r="H4" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" t="s">
+        <v>0</v>
+      </c>
+      <c r="D5" t="s">
+        <v>0</v>
+      </c>
+      <c r="E5" t="s">
+        <v>0</v>
+      </c>
+      <c r="F5" t="s">
+        <v>0</v>
+      </c>
+      <c r="G5" t="s">
+        <v>0</v>
+      </c>
+      <c r="H5" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D6" t="s">
+        <v>0</v>
+      </c>
+      <c r="E6" t="s">
+        <v>0</v>
+      </c>
+      <c r="F6" t="s">
+        <v>0</v>
+      </c>
+      <c r="G6" t="s">
+        <v>0</v>
+      </c>
+      <c r="H6" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" t="s">
+        <v>0</v>
+      </c>
+      <c r="C7" t="s">
+        <v>0</v>
+      </c>
+      <c r="D7" t="s">
+        <v>0</v>
+      </c>
+      <c r="E7" t="s">
+        <v>0</v>
+      </c>
+      <c r="F7" t="s">
+        <v>0</v>
+      </c>
+      <c r="G7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H7" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8" t="s">
+        <v>0</v>
+      </c>
+      <c r="C8" t="s">
+        <v>0</v>
+      </c>
+      <c r="D8" t="s">
+        <v>0</v>
+      </c>
+      <c r="E8" t="s">
+        <v>0</v>
+      </c>
+      <c r="F8" t="s">
+        <v>0</v>
+      </c>
+      <c r="G8" t="s">
+        <v>0</v>
+      </c>
+      <c r="H8" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B9" t="s">
+        <v>0</v>
+      </c>
+      <c r="C9" t="s">
+        <v>0</v>
+      </c>
+      <c r="D9" t="s">
+        <v>0</v>
+      </c>
+      <c r="E9" t="s">
+        <v>0</v>
+      </c>
+      <c r="F9" t="s">
+        <v>0</v>
+      </c>
+      <c r="G9" t="s">
+        <v>0</v>
+      </c>
+      <c r="H9" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B10" t="s">
+        <v>0</v>
+      </c>
+      <c r="C10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D10" t="s">
+        <v>0</v>
+      </c>
+      <c r="E10" t="s">
+        <v>0</v>
+      </c>
+      <c r="F10" t="s">
+        <v>0</v>
+      </c>
+      <c r="G10" t="s">
+        <v>0</v>
+      </c>
+      <c r="H10" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B11" t="s">
+        <v>0</v>
+      </c>
+      <c r="C11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D11" t="s">
+        <v>0</v>
+      </c>
+      <c r="E11" t="s">
+        <v>0</v>
+      </c>
+      <c r="F11" t="s">
+        <v>0</v>
+      </c>
+      <c r="G11" t="s">
+        <v>0</v>
+      </c>
+      <c r="H11" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B12" t="s">
+        <v>0</v>
+      </c>
+      <c r="C12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D12" t="s">
+        <v>0</v>
+      </c>
+      <c r="E12" t="s">
+        <v>0</v>
+      </c>
+      <c r="F12" t="s">
+        <v>0</v>
+      </c>
+      <c r="G12" t="s">
+        <v>0</v>
+      </c>
+      <c r="H12" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>0</v>
+      </c>
+      <c r="B13" t="s">
+        <v>0</v>
+      </c>
+      <c r="C13" t="s">
+        <v>0</v>
+      </c>
+      <c r="D13" t="s">
+        <v>0</v>
+      </c>
+      <c r="E13" t="s">
+        <v>0</v>
+      </c>
+      <c r="F13" t="s">
+        <v>0</v>
+      </c>
+      <c r="G13" t="s">
+        <v>0</v>
+      </c>
+      <c r="H13" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B14" t="s">
+        <v>0</v>
+      </c>
+      <c r="C14" t="s">
+        <v>0</v>
+      </c>
+      <c r="D14" t="s">
+        <v>0</v>
+      </c>
+      <c r="E14" t="s">
+        <v>0</v>
+      </c>
+      <c r="F14" t="s">
+        <v>0</v>
+      </c>
+      <c r="G14" t="s">
+        <v>0</v>
+      </c>
+      <c r="H14" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>0</v>
+      </c>
+      <c r="B15" t="s">
+        <v>0</v>
+      </c>
+      <c r="C15" t="s">
+        <v>0</v>
+      </c>
+      <c r="D15" t="s">
+        <v>0</v>
+      </c>
+      <c r="E15" t="s">
+        <v>0</v>
+      </c>
+      <c r="F15" t="s">
+        <v>0</v>
+      </c>
+      <c r="G15" t="s">
+        <v>0</v>
+      </c>
+      <c r="H15" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>0</v>
+      </c>
+      <c r="B16" t="s">
+        <v>0</v>
+      </c>
+      <c r="C16" t="s">
+        <v>0</v>
+      </c>
+      <c r="D16" t="s">
+        <v>0</v>
+      </c>
+      <c r="E16" t="s">
+        <v>0</v>
+      </c>
+      <c r="F16" t="s">
+        <v>0</v>
+      </c>
+      <c r="G16" t="s">
+        <v>0</v>
+      </c>
+      <c r="H16" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>0</v>
+      </c>
+      <c r="B17" t="s">
+        <v>0</v>
+      </c>
+      <c r="C17" t="s">
+        <v>0</v>
+      </c>
+      <c r="D17" t="s">
+        <v>0</v>
+      </c>
+      <c r="E17" t="s">
+        <v>0</v>
+      </c>
+      <c r="F17" t="s">
+        <v>0</v>
+      </c>
+      <c r="G17" t="s">
+        <v>0</v>
+      </c>
+      <c r="H17" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>0</v>
+      </c>
+      <c r="B18" t="s">
+        <v>0</v>
+      </c>
+      <c r="C18" t="s">
+        <v>0</v>
+      </c>
+      <c r="D18" t="s">
+        <v>0</v>
+      </c>
+      <c r="E18" t="s">
+        <v>0</v>
+      </c>
+      <c r="F18" t="s">
+        <v>0</v>
+      </c>
+      <c r="G18" t="s">
+        <v>0</v>
+      </c>
+      <c r="H18" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>0</v>
+      </c>
+      <c r="B19" t="s">
+        <v>0</v>
+      </c>
+      <c r="C19" t="s">
+        <v>0</v>
+      </c>
+      <c r="D19" t="s">
+        <v>0</v>
+      </c>
+      <c r="E19" t="s">
+        <v>0</v>
+      </c>
+      <c r="F19" t="s">
+        <v>0</v>
+      </c>
+      <c r="G19" t="s">
+        <v>0</v>
+      </c>
+      <c r="H19" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>0</v>
+      </c>
+      <c r="B20" t="s">
+        <v>0</v>
+      </c>
+      <c r="C20" t="s">
+        <v>0</v>
+      </c>
+      <c r="D20" t="s">
+        <v>0</v>
+      </c>
+      <c r="E20" t="s">
+        <v>0</v>
+      </c>
+      <c r="F20" t="s">
+        <v>0</v>
+      </c>
+      <c r="G20" t="s">
+        <v>0</v>
+      </c>
+      <c r="H20" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>0</v>
+      </c>
+      <c r="B21" t="s">
+        <v>0</v>
+      </c>
+      <c r="C21" t="s">
+        <v>0</v>
+      </c>
+      <c r="D21" t="s">
+        <v>0</v>
+      </c>
+      <c r="E21" t="s">
+        <v>0</v>
+      </c>
+      <c r="F21" t="s">
+        <v>0</v>
+      </c>
+      <c r="G21" t="s">
+        <v>0</v>
+      </c>
+      <c r="H21" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>0</v>
+      </c>
+      <c r="B22" t="s">
+        <v>0</v>
+      </c>
+      <c r="C22" t="s">
+        <v>0</v>
+      </c>
+      <c r="D22" t="s">
+        <v>0</v>
+      </c>
+      <c r="E22" t="s">
+        <v>0</v>
+      </c>
+      <c r="F22" t="s">
+        <v>0</v>
+      </c>
+      <c r="G22" t="s">
+        <v>0</v>
+      </c>
+      <c r="H22" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>0</v>
+      </c>
+      <c r="B23" t="s">
+        <v>0</v>
+      </c>
+      <c r="C23" t="s">
+        <v>0</v>
+      </c>
+      <c r="D23" t="s">
+        <v>0</v>
+      </c>
+      <c r="E23" t="s">
+        <v>0</v>
+      </c>
+      <c r="F23" t="s">
+        <v>0</v>
+      </c>
+      <c r="G23" t="s">
+        <v>0</v>
+      </c>
+      <c r="H23" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>0</v>
+      </c>
+      <c r="B24" t="s">
+        <v>0</v>
+      </c>
+      <c r="C24" t="s">
+        <v>0</v>
+      </c>
+      <c r="D24" t="s">
+        <v>0</v>
+      </c>
+      <c r="E24" t="s">
+        <v>0</v>
+      </c>
+      <c r="F24" t="s">
+        <v>0</v>
+      </c>
+      <c r="G24" t="s">
+        <v>0</v>
+      </c>
+      <c r="H24" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>0</v>
+      </c>
+      <c r="B25" t="s">
+        <v>0</v>
+      </c>
+      <c r="C25" t="s">
+        <v>0</v>
+      </c>
+      <c r="D25" t="s">
+        <v>0</v>
+      </c>
+      <c r="E25" t="s">
+        <v>0</v>
+      </c>
+      <c r="F25" t="s">
+        <v>0</v>
+      </c>
+      <c r="G25" t="s">
+        <v>0</v>
+      </c>
+      <c r="H25" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>0</v>
+      </c>
+      <c r="B26" t="s">
+        <v>0</v>
+      </c>
+      <c r="C26" t="s">
+        <v>0</v>
+      </c>
+      <c r="D26" t="s">
+        <v>0</v>
+      </c>
+      <c r="E26" t="s">
+        <v>0</v>
+      </c>
+      <c r="F26" t="s">
+        <v>0</v>
+      </c>
+      <c r="G26" t="s">
+        <v>0</v>
+      </c>
+      <c r="H26" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>0</v>
+      </c>
+      <c r="B27" t="s">
+        <v>0</v>
+      </c>
+      <c r="C27" t="s">
+        <v>0</v>
+      </c>
+      <c r="D27" t="s">
+        <v>0</v>
+      </c>
+      <c r="E27" t="s">
+        <v>0</v>
+      </c>
+      <c r="F27" t="s">
+        <v>0</v>
+      </c>
+      <c r="G27" t="s">
+        <v>0</v>
+      </c>
+      <c r="H27" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>0</v>
+      </c>
+      <c r="B28" t="s">
+        <v>0</v>
+      </c>
+      <c r="C28" t="s">
+        <v>0</v>
+      </c>
+      <c r="D28" t="s">
+        <v>0</v>
+      </c>
+      <c r="E28" t="s">
+        <v>0</v>
+      </c>
+      <c r="F28" t="s">
+        <v>0</v>
+      </c>
+      <c r="G28" t="s">
+        <v>0</v>
+      </c>
+      <c r="H28" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>0</v>
+      </c>
+      <c r="B29" t="s">
+        <v>0</v>
+      </c>
+      <c r="C29" t="s">
+        <v>0</v>
+      </c>
+      <c r="D29" t="s">
+        <v>0</v>
+      </c>
+      <c r="E29" t="s">
+        <v>0</v>
+      </c>
+      <c r="F29" t="s">
+        <v>0</v>
+      </c>
+      <c r="G29" t="s">
+        <v>0</v>
+      </c>
+      <c r="H29" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>0</v>
+      </c>
+      <c r="B30" t="s">
+        <v>0</v>
+      </c>
+      <c r="C30" t="s">
+        <v>0</v>
+      </c>
+      <c r="D30" t="s">
+        <v>0</v>
+      </c>
+      <c r="E30" t="s">
+        <v>0</v>
+      </c>
+      <c r="F30" t="s">
+        <v>0</v>
+      </c>
+      <c r="G30" t="s">
+        <v>0</v>
+      </c>
+      <c r="H30" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>0</v>
+      </c>
+      <c r="B31" t="s">
+        <v>0</v>
+      </c>
+      <c r="C31" t="s">
+        <v>0</v>
+      </c>
+      <c r="D31" t="s">
+        <v>0</v>
+      </c>
+      <c r="E31" t="s">
+        <v>0</v>
+      </c>
+      <c r="F31" t="s">
+        <v>0</v>
+      </c>
+      <c r="G31" t="s">
+        <v>0</v>
+      </c>
+      <c r="H31" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>0</v>
+      </c>
+      <c r="B32" t="s">
+        <v>0</v>
+      </c>
+      <c r="C32" t="s">
+        <v>0</v>
+      </c>
+      <c r="D32" t="s">
+        <v>0</v>
+      </c>
+      <c r="E32" t="s">
+        <v>0</v>
+      </c>
+      <c r="F32" t="s">
+        <v>0</v>
+      </c>
+      <c r="G32" t="s">
+        <v>0</v>
+      </c>
+      <c r="H32" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>0</v>
+      </c>
+      <c r="B33" t="s">
+        <v>0</v>
+      </c>
+      <c r="C33" t="s">
+        <v>0</v>
+      </c>
+      <c r="D33" t="s">
+        <v>0</v>
+      </c>
+      <c r="E33" t="s">
+        <v>0</v>
+      </c>
+      <c r="F33" t="s">
+        <v>0</v>
+      </c>
+      <c r="G33" t="s">
+        <v>0</v>
+      </c>
+      <c r="H33" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>0</v>
+      </c>
+      <c r="B34" t="s">
+        <v>0</v>
+      </c>
+      <c r="C34" t="s">
+        <v>0</v>
+      </c>
+      <c r="D34" t="s">
+        <v>0</v>
+      </c>
+      <c r="E34" t="s">
+        <v>0</v>
+      </c>
+      <c r="F34" t="s">
+        <v>0</v>
+      </c>
+      <c r="G34" t="s">
+        <v>0</v>
+      </c>
+      <c r="H34" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>0</v>
+      </c>
+      <c r="B35" t="s">
+        <v>0</v>
+      </c>
+      <c r="C35" t="s">
+        <v>0</v>
+      </c>
+      <c r="D35" t="s">
+        <v>0</v>
+      </c>
+      <c r="E35" t="s">
+        <v>0</v>
+      </c>
+      <c r="F35" t="s">
+        <v>0</v>
+      </c>
+      <c r="G35" t="s">
+        <v>0</v>
+      </c>
+      <c r="H35" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>0</v>
+      </c>
+      <c r="B36" t="s">
+        <v>0</v>
+      </c>
+      <c r="C36" t="s">
+        <v>0</v>
+      </c>
+      <c r="D36" t="s">
+        <v>0</v>
+      </c>
+      <c r="E36" t="s">
+        <v>0</v>
+      </c>
+      <c r="F36" t="s">
+        <v>0</v>
+      </c>
+      <c r="G36" t="s">
+        <v>0</v>
+      </c>
+      <c r="H36" t="s">
         <v>0</v>
       </c>
     </row>

--- a/tt.xlsx
+++ b/tt.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ethan.li\Documents\test_bc_in_sourcetree\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ethan.li\Documents\temp\test_bc_in_sourcetree\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{017502E3-8C61-45D3-B84E-54B77DA1A221}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CFC9256-96E6-47A2-9F67-5681CFA57F59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3456" yWindow="3456" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,9 +28,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="1">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="1">
   <si>
-    <t>a</t>
+    <t>b</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -356,10 +356,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H36"/>
+  <dimension ref="A1:I36"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -384,8 +384,11 @@
       <c r="H1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -410,8 +413,11 @@
       <c r="H2" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -436,8 +442,11 @@
       <c r="H3" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -462,8 +471,11 @@
       <c r="H4" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I4" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>0</v>
       </c>
@@ -488,8 +500,11 @@
       <c r="H5" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I5" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>0</v>
       </c>
@@ -514,8 +529,11 @@
       <c r="H6" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I6" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>0</v>
       </c>
@@ -540,8 +558,11 @@
       <c r="H7" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I7" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>0</v>
       </c>
@@ -566,8 +587,11 @@
       <c r="H8" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I8" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>0</v>
       </c>
@@ -592,8 +616,11 @@
       <c r="H9" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I9" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>0</v>
       </c>
@@ -618,8 +645,11 @@
       <c r="H10" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I10" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>0</v>
       </c>
@@ -644,8 +674,11 @@
       <c r="H11" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I11" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>0</v>
       </c>
@@ -670,8 +703,11 @@
       <c r="H12" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I12" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>0</v>
       </c>
@@ -696,8 +732,11 @@
       <c r="H13" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I13" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>0</v>
       </c>
@@ -722,8 +761,11 @@
       <c r="H14" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I14" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>0</v>
       </c>
@@ -748,8 +790,11 @@
       <c r="H15" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I15" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>0</v>
       </c>
@@ -774,8 +819,11 @@
       <c r="H16" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I16" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>0</v>
       </c>
@@ -800,8 +848,11 @@
       <c r="H17" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I17" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>0</v>
       </c>
@@ -826,8 +877,11 @@
       <c r="H18" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I18" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>0</v>
       </c>
@@ -852,8 +906,11 @@
       <c r="H19" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I19" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>0</v>
       </c>
@@ -878,8 +935,11 @@
       <c r="H20" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I20" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>0</v>
       </c>
@@ -904,8 +964,11 @@
       <c r="H21" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I21" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>0</v>
       </c>
@@ -930,8 +993,11 @@
       <c r="H22" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I22" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>0</v>
       </c>
@@ -956,8 +1022,11 @@
       <c r="H23" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I23" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>0</v>
       </c>
@@ -982,8 +1051,11 @@
       <c r="H24" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I24" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>0</v>
       </c>
@@ -1008,8 +1080,11 @@
       <c r="H25" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I25" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>0</v>
       </c>
@@ -1034,8 +1109,11 @@
       <c r="H26" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I26" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>0</v>
       </c>
@@ -1060,8 +1138,11 @@
       <c r="H27" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I27" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>0</v>
       </c>
@@ -1086,8 +1167,11 @@
       <c r="H28" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I28" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>0</v>
       </c>
@@ -1112,8 +1196,11 @@
       <c r="H29" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I29" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>0</v>
       </c>
@@ -1138,8 +1225,11 @@
       <c r="H30" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I30" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>0</v>
       </c>
@@ -1164,8 +1254,11 @@
       <c r="H31" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I31" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>0</v>
       </c>
@@ -1190,8 +1283,11 @@
       <c r="H32" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I32" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>0</v>
       </c>
@@ -1216,8 +1312,11 @@
       <c r="H33" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I33" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>0</v>
       </c>
@@ -1242,8 +1341,11 @@
       <c r="H34" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I34" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>0</v>
       </c>
@@ -1268,8 +1370,11 @@
       <c r="H35" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I35" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>0</v>
       </c>
@@ -1292,6 +1397,9 @@
         <v>0</v>
       </c>
       <c r="H36" t="s">
+        <v>0</v>
+      </c>
+      <c r="I36" t="s">
         <v>0</v>
       </c>
     </row>

--- a/tt.xlsx
+++ b/tt.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ethan.li\Documents\test_bc_in_sourcetree\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{017502E3-8C61-45D3-B84E-54B77DA1A221}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EADD65AE-7D98-42BE-8A16-BFF814D9A148}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3456" yWindow="3456" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,9 +28,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="1">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="1">
   <si>
-    <t>a</t>
+    <t>c</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -356,7 +356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H36"/>
+  <dimension ref="A1:H37"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -1292,6 +1292,32 @@
         <v>0</v>
       </c>
       <c r="H36" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>0</v>
+      </c>
+      <c r="B37" t="s">
+        <v>0</v>
+      </c>
+      <c r="C37" t="s">
+        <v>0</v>
+      </c>
+      <c r="D37" t="s">
+        <v>0</v>
+      </c>
+      <c r="E37" t="s">
+        <v>0</v>
+      </c>
+      <c r="F37" t="s">
+        <v>0</v>
+      </c>
+      <c r="G37" t="s">
+        <v>0</v>
+      </c>
+      <c r="H37" t="s">
         <v>0</v>
       </c>
     </row>
